--- a/tests/corpus/xlsx/l2_print.xlsx
+++ b/tests/corpus/xlsx/l2_print.xlsx
@@ -76,7 +76,24 @@
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="A1">
+    <cfRule type="expression" priority="1">
+      <formula>A1&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation type="whole" sqref="A1">
+      <formula1>0</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9"/>
+  <extLst>
+    <ext uri="{sparkline-test}">
+      <x14:sparklineGroups xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main">
+        <x14:sparklineGroup/>
+      </x14:sparklineGroups>
+    </ext>
+  </extLst>
 </worksheet>
 </file>